--- a/output/full_scan/batch_seq6_2026-07-16.xlsx
+++ b/output/full_scan/batch_seq6_2026-07-16.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O116"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -845,21 +845,21 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6270</v>
+        <v>6226</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>627.8697801697297</v>
+        <v>637.9272041672829</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>33.2</v>
+        <v>25.05</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>44.30678931563941</v>
+        <v>63.88848559186821</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>40.91720835868778</v>
+        <v>40.07134384141721</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1853197778476514</v>
+        <v>0.4009484150788437</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.9031959133880708</v>
+        <v>0.2796901921638923</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6182</v>
+        <v>6270</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>596.2180134033872</v>
+        <v>627.8697801697297</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>166</v>
+        <v>33.2</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>63.02228006012598</v>
+        <v>44.30678931563941</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>42.30687452404304</v>
+        <v>40.91720835868778</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.9647172913152268</v>
+        <v>0.1853197778476514</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.909753249944956</v>
+        <v>-0.9031959133880708</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6165</v>
+        <v>6182</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>592.8215305698017</v>
+        <v>596.2180134033872</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>50.9</v>
+        <v>166</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>58.79256004920597</v>
+        <v>63.02228006012598</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>21.04534843949388</v>
+        <v>42.30687452404304</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.9239621226275004</v>
+        <v>0.9647172913152268</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2461459433906958</v>
+        <v>1.909753249944956</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6409</v>
+        <v>6165</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>587.0097883286476</v>
+        <v>592.8215305698017</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1020</v>
+        <v>50.9</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>49.83478966270036</v>
+        <v>58.79256004920597</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>41.19535305880876</v>
+        <v>21.04534843949388</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.4951114543417994</v>
+        <v>0.9239621226275004</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-19.32642471895018</v>
+        <v>0.2461459433906958</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6241</v>
+        <v>6409</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>576.0000879346283</v>
+        <v>587.0097883286476</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>17.7</v>
+        <v>1020</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>69.05615335131166</v>
+        <v>49.83478966270036</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46.0417378837694</v>
+        <v>41.19535305880876</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.699701884453313</v>
+        <v>0.4951114543417994</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.1945932934364045</v>
+        <v>-19.32642471895018</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6202</v>
+        <v>6241</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>574.9217158670637</v>
+        <v>576.0000879346283</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>17.7</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>48.29485583586131</v>
+        <v>69.05615335131166</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>25.51069188425878</v>
+        <v>46.0417378837694</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.8178636976931296</v>
+        <v>1.699701884453313</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.4406303246896428</v>
+        <v>0.1945932934364045</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6464</v>
+        <v>6202</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>574.0736276245536</v>
+        <v>574.9217158670637</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>57.57613131960055</v>
+        <v>48.29485583586131</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22.96405316887853</v>
+        <v>25.51069188425878</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.5574539702724322</v>
+        <v>0.8178636976931296</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0830578680917446</v>
+        <v>-0.4406303246896428</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6432</v>
+        <v>6464</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>574.0081592462723</v>
+        <v>574.0736276245536</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>73</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>50.25093530852486</v>
+        <v>57.57613131960055</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>23.3500622632809</v>
+        <v>22.96405316887853</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.3071673318810959</v>
+        <v>0.5574539702724322</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-1.275263587555504</v>
+        <v>0.0830578680917446</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6220</v>
+        <v>6432</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>555.9601412291933</v>
+        <v>574.0081592462723</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>35.1</v>
+        <v>73</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>51.53633211938531</v>
+        <v>50.25093530852486</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>35.82822138124612</v>
+        <v>23.3500622632809</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.3848383956588181</v>
+        <v>0.3071673318810959</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.1285825780187134</v>
+        <v>-1.275263587555504</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6477</v>
+        <v>6220</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>550.0368624309872</v>
+        <v>555.9601412291933</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>41</v>
+        <v>35.1</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>64.09718453673183</v>
+        <v>51.53633211938531</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>30.23329251981512</v>
+        <v>35.82822138124612</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.003686243098716</v>
+        <v>0.3848383956588181</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.8731331829106495</v>
+        <v>-0.1285825780187134</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6274</v>
+        <v>6477</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>549.5144325809113</v>
+        <v>550.0368624309872</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1295</v>
+        <v>41</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>37.33369868753735</v>
+        <v>64.09718453673183</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>20.32631379199456</v>
+        <v>30.23329251981512</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.575427385716864</v>
+        <v>1.003686243098716</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-50.08139088692808</v>
+        <v>0.8731331829106495</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6446</v>
+        <v>6274</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>538.1794438056057</v>
+        <v>549.5144325809113</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1260</v>
+        <v>1295</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>54.15582267123729</v>
+        <v>37.33369868753735</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>43.56552334952083</v>
+        <v>20.32631379199456</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.326417774692736</v>
+        <v>1.575427385716864</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-24.71915037411476</v>
+        <v>-50.08139088692808</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6261</v>
+        <v>6446</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>509.0865186707198</v>
+        <v>538.1794438056057</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>1260</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>41.4531377373798</v>
+        <v>54.15582267123729</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>19.57841700793683</v>
+        <v>43.56552334952083</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.4828131244503895</v>
+        <v>1.326417774692736</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0471861870306593</v>
+        <v>-24.71915037411476</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6259</v>
+        <v>6261</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>508.0869315396434</v>
+        <v>509.0865186707198</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>36.85</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>53.30328738110408</v>
+        <v>41.4531377373798</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>31.30283566803016</v>
+        <v>19.57841700793683</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.8091526631629807</v>
+        <v>0.4828131244503895</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.7195462030645761</v>
+        <v>0.0471861870306593</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6177</v>
+        <v>6259</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>500.4844534471359</v>
+        <v>508.0869315396434</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>48</v>
+        <v>36.85</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>61.77076919090953</v>
+        <v>53.30328738110408</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20.75515961690662</v>
+        <v>31.30283566803016</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8856369667816759</v>
+        <v>0.8091526631629807</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1481413420607895</v>
+        <v>-0.7195462030645761</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6214</v>
+        <v>6177</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>497.6751278123524</v>
+        <v>500.4844534471359</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>55.20781411741768</v>
+        <v>61.77076919090953</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>14.6839404194137</v>
+        <v>20.75515961690662</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5441427367448555</v>
+        <v>0.8856369667816759</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.6693694407345943</v>
+        <v>0.1481413420607895</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6257</v>
+        <v>6214</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>485.2148215046378</v>
+        <v>497.6751278123524</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>238</v>
+        <v>140</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>52.01046422572692</v>
+        <v>55.20781411741768</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>18.5012864355623</v>
+        <v>14.6839404194137</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.365853426475073</v>
+        <v>0.5441427367448555</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-2.173149101310193</v>
+        <v>0.6693694407345943</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6472</v>
+        <v>6257</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>479.0529145001126</v>
+        <v>485.2148215046378</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>415.5</v>
+        <v>238</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>49.90871062110276</v>
+        <v>52.01046422572692</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>31.25530608806548</v>
+        <v>18.5012864355623</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.13007208852447</v>
+        <v>0.365853426475073</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-2.45118469586852</v>
+        <v>-2.173149101310193</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6197</v>
+        <v>6472</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>477.0301372219466</v>
+        <v>479.0529145001126</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>325.5</v>
+        <v>415.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46.5006142403149</v>
+        <v>49.90871062110276</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31.23063636537172</v>
+        <v>31.25530608806548</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4330341378854165</v>
+        <v>1.13007208852447</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-7.862404571245392</v>
+        <v>-2.45118469586852</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6191</v>
+        <v>6197</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>474.2656727642572</v>
+        <v>477.0301372219466</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>93.5</v>
+        <v>325.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>39.74411215746296</v>
+        <v>46.5006142403149</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>23.28785259736478</v>
+        <v>31.23063636537172</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.3695147806603653</v>
+        <v>0.4330341378854165</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-1.355452940798779</v>
+        <v>-7.862404571245392</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6173</v>
+        <v>6191</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>474.1547322629239</v>
+        <v>474.2656727642572</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>215.5</v>
+        <v>93.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>39.07482767074505</v>
+        <v>39.74411215746296</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26.74854022041764</v>
+        <v>23.28785259736478</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.097900767005303</v>
+        <v>0.3695147806603653</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-15.1502417260717</v>
+        <v>-1.355452940798779</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6183</v>
+        <v>6173</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>470.7951133383658</v>
+        <v>474.1547322629239</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>215.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>58.73702638981439</v>
+        <v>39.07482767074505</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>14.03740211779363</v>
+        <v>26.74854022041764</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.663965686258545</v>
+        <v>1.097900767005303</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.1992212240786727</v>
+        <v>-15.1502417260717</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6284</v>
+        <v>6183</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>455.2698505191622</v>
+        <v>470.7951133383658</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>88.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>39.24547311105807</v>
+        <v>58.73702638981439</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25.62396875988872</v>
+        <v>14.03740211779363</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.3675179146675841</v>
+        <v>0.663965686258545</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-1.743429309179038</v>
+        <v>0.1992212240786727</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6271</v>
+        <v>6284</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>455.0626440154901</v>
+        <v>455.2698505191622</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>224</v>
+        <v>88.8</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>43.84774981046913</v>
+        <v>39.24547311105807</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20.81344251977527</v>
+        <v>25.62396875988872</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.4441826985259674</v>
+        <v>0.3675179146675841</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-6.438299448712881</v>
+        <v>-1.743429309179038</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6166</v>
+        <v>6271</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>451.2721719945711</v>
+        <v>455.0626440154901</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>128</v>
+        <v>224</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>44.85876439294768</v>
+        <v>43.84774981046913</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>29.59615840876982</v>
+        <v>20.81344251977527</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.4111361537801696</v>
+        <v>0.4441826985259674</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-2.199060360214266</v>
+        <v>-6.438299448712881</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6190</v>
+        <v>6166</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>445.5637629630471</v>
+        <v>451.2721719945711</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>75.2</v>
+        <v>128</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>40.26895660278721</v>
+        <v>44.85876439294768</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>17.95652582789592</v>
+        <v>29.59615840876982</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4787553166840304</v>
+        <v>0.4111361537801696</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-1.123217296348709</v>
+        <v>-2.199060360214266</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6435</v>
+        <v>6190</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>441.0803990851726</v>
+        <v>445.5637629630471</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>308.5</v>
+        <v>75.2</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,49 +2248,49 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>44.09289386086668</v>
+        <v>40.26895660278721</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>29.19376595126109</v>
+        <v>17.95652582789592</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.308039908517263</v>
+        <v>0.4787553166840304</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-10.77667457157996</v>
+        <v>-1.123217296348709</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6244</v>
+        <v>6435</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>439.5607418324305</v>
+        <v>441.0803990851726</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>26.5</v>
+        <v>308.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>44.03941643040615</v>
+        <v>44.09289386086668</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>10.96644673658468</v>
+        <v>29.19376595126109</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4526737382773655</v>
+        <v>0.308039908517263</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0218651017678717</v>
+        <v>-10.77667457157996</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6223</v>
+        <v>6244</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>439.2315246455881</v>
+        <v>439.5607418324305</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>6220</v>
+        <v>26.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>47.34520518455846</v>
+        <v>44.03941643040615</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>22.61725234996416</v>
+        <v>10.96644673658468</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7349724244996386</v>
+        <v>0.4526737382773655</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-93.96164752501372</v>
+        <v>-0.0218651017678717</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6209</v>
+        <v>6223</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>437.8348086516065</v>
+        <v>439.2315246455881</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>76.90000000000001</v>
+        <v>6220</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>43.98778268252838</v>
+        <v>47.34520518455846</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>21.60229165481458</v>
+        <v>22.61725234996416</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.2796814347634176</v>
+        <v>0.7349724244996386</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.8878898372309791</v>
+        <v>-93.96164752501372</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6208</v>
+        <v>6209</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>434.8711697789306</v>
+        <v>437.8348086516065</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>88.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>46.56764502260626</v>
+        <v>43.98778268252838</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>16.63968125403662</v>
+        <v>21.60229165481458</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.2971797745559585</v>
+        <v>0.2796814347634176</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-1.284926571355778</v>
+        <v>-0.8878898372309791</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6419</v>
+        <v>6208</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>434.5642489337414</v>
+        <v>434.8711697789306</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>143.5</v>
+        <v>88.3</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.07168431964394</v>
+        <v>46.56764502260626</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>8.950738745104386</v>
+        <v>16.63968125403662</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4716096377203607</v>
+        <v>0.2971797745559585</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.2828578981897254</v>
+        <v>-1.284926571355778</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6192</v>
+        <v>6419</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>433.9705926814327</v>
+        <v>434.5642489337414</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>120.5</v>
+        <v>143.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>48.3857512599251</v>
+        <v>49.07168431964394</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20.06192361715221</v>
+        <v>8.950738745104386</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.2883449881128221</v>
+        <v>0.4716096377203607</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1836314348243632</v>
+        <v>-0.2828578981897254</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6215</v>
+        <v>6192</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>430.4178679627865</v>
+        <v>433.9705926814327</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>106</v>
+        <v>120.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>44.31789641375676</v>
+        <v>48.3857512599251</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15.87259953896514</v>
+        <v>20.06192361715221</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.2703664824702141</v>
+        <v>0.2883449881128221</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.112513408093827</v>
+        <v>0.1836314348243632</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6423</v>
+        <v>6215</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>427.0255149927497</v>
+        <v>430.4178679627865</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>72.3</v>
+        <v>106</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>33.02837398518126</v>
+        <v>44.31789641375676</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>25.71049236332405</v>
+        <v>15.87259953896514</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.2733092818529367</v>
+        <v>0.2703664824702141</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.4905436252569717</v>
+        <v>-0.112513408093827</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6207</v>
+        <v>6423</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>414.0464921820769</v>
+        <v>427.0255149927497</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>140.5</v>
+        <v>72.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.05997006390822</v>
+        <v>33.02837398518126</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>38.52869306592115</v>
+        <v>25.71049236332405</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.9442480517467476</v>
+        <v>0.2733092818529367</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-2.912279882414654</v>
+        <v>-0.4905436252569717</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6213</v>
+        <v>6207</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>409.8025690434762</v>
+        <v>414.0464921820769</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>325</v>
+        <v>140.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>48.44829736197333</v>
+        <v>51.05997006390822</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.51021005731371</v>
+        <v>38.52869306592115</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4344587312776274</v>
+        <v>0.9442480517467476</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-6.392033741235501</v>
+        <v>-2.912279882414654</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6235</v>
+        <v>6213</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>406.4758927667898</v>
+        <v>409.8025690434762</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>42.35</v>
+        <v>325</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>50.32945194355077</v>
+        <v>48.44829736197333</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.13229650092031</v>
+        <v>22.51021005731371</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5775493642718251</v>
+        <v>0.4344587312776274</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.1921355117238024</v>
+        <v>-6.392033741235501</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6426</v>
+        <v>6235</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>389.1115351961358</v>
+        <v>406.4758927667898</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>171</v>
+        <v>42.35</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>35.70772685603222</v>
+        <v>50.32945194355077</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21.16750270058574</v>
+        <v>21.13229650092031</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.3523012248161564</v>
+        <v>0.5775493642718251</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.7773463446962818</v>
+        <v>0.1921355117238024</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6277</v>
+        <v>6426</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>384.0125560071617</v>
+        <v>389.1115351961358</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>74.2</v>
+        <v>171</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>58.55280928232497</v>
+        <v>35.70772685603222</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>26.71698866562136</v>
+        <v>21.16750270058574</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.9539879997159508</v>
+        <v>0.3523012248161564</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.5707991538424959</v>
+        <v>-0.7773463446962818</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6229</v>
+        <v>6277</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>383.7539753699644</v>
+        <v>384.0125560071617</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>25.25</v>
+        <v>74.2</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>41.0962173314306</v>
+        <v>58.55280928232497</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>12.30658245550459</v>
+        <v>26.71698866562136</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3079609892576286</v>
+        <v>0.9539879997159508</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.1984585773388914</v>
+        <v>0.5707991538424959</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6465</v>
+        <v>6229</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>381.6267623724013</v>
+        <v>383.7539753699644</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>56.4</v>
+        <v>25.25</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>44.0721032393268</v>
+        <v>41.0962173314306</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>21.16650392048677</v>
+        <v>12.30658245550459</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.2648357296613906</v>
+        <v>0.3079609892576286</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-1.170613118485692</v>
+        <v>-0.1984585773388914</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6204</v>
+        <v>6465</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>374.4390798525611</v>
+        <v>381.6267623724013</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>84.09999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>33.04985163787653</v>
+        <v>44.0721032393268</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>29.24643823356537</v>
+        <v>21.16650392048677</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.2689822261911752</v>
+        <v>0.2648357296613906</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-4.990191473782902</v>
+        <v>-1.170613118485692</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6187</v>
+        <v>6204</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>373.9323249116358</v>
+        <v>374.4390798525611</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>1075</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,49 +3149,49 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>51.03661208140134</v>
+        <v>33.04985163787653</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>9.430492469525795</v>
+        <v>29.24643823356537</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.640417285335365</v>
+        <v>0.2689822261911752</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>4.61049831144549</v>
+        <v>-4.990191473782902</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6282</v>
+        <v>6187</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>372.7990267606776</v>
+        <v>373.9323249116358</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>53</v>
+        <v>1075</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,49 +3202,49 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>41.88610459137544</v>
+        <v>51.03661208140134</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>19.44509412019578</v>
+        <v>9.430492469525795</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8485458494408293</v>
+        <v>1.640417285335365</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.564877843517366</v>
+        <v>4.61049831144549</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6245</v>
+        <v>6282</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>366.1247530235995</v>
+        <v>372.7990267606776</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>80.59999999999999</v>
+        <v>53</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>47.57650200102632</v>
+        <v>41.88610459137544</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>9.895275236014371</v>
+        <v>19.44509412019578</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.796398156106599</v>
+        <v>0.8485458494408293</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1942167533958199</v>
+        <v>-0.564877843517366</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6449</v>
+        <v>6245</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>366.1002916655608</v>
+        <v>366.1247530235995</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>278</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>37.74913422697461</v>
+        <v>47.57650200102632</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>20.13624165540077</v>
+        <v>9.895275236014371</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.5434716999912821</v>
+        <v>0.796398156106599</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-10.75935433657551</v>
+        <v>0.1942167533958199</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6164</v>
+        <v>6449</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>365.7721873757285</v>
+        <v>366.1002916655608</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>13.65</v>
+        <v>278</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>48.16231276997989</v>
+        <v>37.74913422697461</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>21.78718786008401</v>
+        <v>20.13624165540077</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.477218737572848</v>
+        <v>0.5434716999912821</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.1659562057363182</v>
+        <v>-10.75935433657551</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6279</v>
+        <v>6164</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>361.8330391545634</v>
+        <v>365.7721873757285</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>119.5</v>
+        <v>13.65</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.23399102147197</v>
+        <v>48.16231276997989</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>18.21775467109346</v>
+        <v>21.78718786008401</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.2966118617329754</v>
+        <v>0.477218737572848</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1834138835309389</v>
+        <v>-0.1659562057363182</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6451</v>
+        <v>6279</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>360.2891655755218</v>
+        <v>361.8330391545634</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>477</v>
+        <v>119.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>42.3319106670961</v>
+        <v>48.23399102147197</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>20.16344084891528</v>
+        <v>18.21775467109346</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.6762542098254906</v>
+        <v>0.2966118617329754</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-9.881478470060916</v>
+        <v>-0.1834138835309389</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6411</v>
+        <v>6451</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>358.9737130275408</v>
+        <v>360.2891655755218</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>86.2</v>
+        <v>477</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>37.79864625574724</v>
+        <v>42.3319106670961</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>20.94232479813135</v>
+        <v>20.16344084891528</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.321810888388191</v>
+        <v>0.6762542098254906</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-1.900886536109106</v>
+        <v>-9.881478470060916</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6285</v>
+        <v>6411</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>357.569360415801</v>
+        <v>358.9737130275408</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>257</v>
+        <v>86.2</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>48.56841855332309</v>
+        <v>37.79864625574724</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>15.74857736378436</v>
+        <v>20.94232479813135</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6632618685053291</v>
+        <v>0.321810888388191</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>1.17805898667069</v>
+        <v>-1.900886536109106</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6218</v>
+        <v>6285</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>355.1603586242671</v>
+        <v>357.569360415801</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>37.25</v>
+        <v>257</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.53410309063801</v>
+        <v>48.56841855332309</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>12.3796865144831</v>
+        <v>15.74857736378436</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6767857531500898</v>
+        <v>0.6632618685053291</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0515856371386788</v>
+        <v>1.17805898667069</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6210</v>
+        <v>6218</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>352.2067962911704</v>
+        <v>355.1603586242671</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>19.9</v>
+        <v>37.25</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>47.74703411410755</v>
+        <v>52.53410309063801</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>26.84045016267881</v>
+        <v>12.3796865144831</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.2378624672285881</v>
+        <v>0.6767857531500898</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0112418846025366</v>
+        <v>0.0515856371386788</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6417</v>
+        <v>6210</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>348.171866066699</v>
+        <v>352.2067962911704</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>123.5</v>
+        <v>19.9</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>37.01364355434026</v>
+        <v>47.74703411410755</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>12.95032752235552</v>
+        <v>26.84045016267881</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5516987127346941</v>
+        <v>0.2378624672285881</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-1.030113717977978</v>
+        <v>-0.0112418846025366</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6442</v>
+        <v>6417</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>347.0608057415299</v>
+        <v>348.171866066699</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>1350</v>
+        <v>123.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>34.50057024614735</v>
+        <v>37.01364355434026</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.23885936081656</v>
+        <v>12.95032752235552</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.4836410247747495</v>
+        <v>0.5516987127346941</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-26.393480386318</v>
+        <v>-1.030113717977978</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6265</v>
+        <v>6442</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>346.1578433219097</v>
+        <v>347.0608057415299</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>51.7</v>
+        <v>1350</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.37670730069975</v>
+        <v>34.50057024614735</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15.18197808745803</v>
+        <v>23.23885936081656</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.56556230778204</v>
+        <v>0.4836410247747495</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.2292836991055645</v>
+        <v>-26.393480386318</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6201</v>
+        <v>6265</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>344.3455856925362</v>
+        <v>346.1578433219097</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>49</v>
+        <v>51.7</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>54.2103991663965</v>
+        <v>47.37670730069975</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>10.10677857500612</v>
+        <v>15.18197808745803</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5298407461740852</v>
+        <v>0.56556230778204</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0871896998596057</v>
+        <v>-0.2292836991055645</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6278</v>
+        <v>6201</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>334.3831840966014</v>
+        <v>344.3455856925362</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>177.5</v>
+        <v>49</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>39.45486020132588</v>
+        <v>54.2103991663965</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>17.98894759561554</v>
+        <v>10.10677857500612</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5332147501013581</v>
+        <v>0.5298407461740852</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-3.636394523963325</v>
+        <v>0.0871896998596057</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6168</v>
+        <v>6278</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>333.5252251130999</v>
+        <v>334.3831840966014</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>26.75</v>
+        <v>177.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>43.0011118124153</v>
+        <v>39.45486020132588</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>20.85732625886648</v>
+        <v>17.98894759561554</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.1987404294817054</v>
+        <v>0.5332147501013581</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.5252970654643283</v>
+        <v>-3.636394523963325</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6474</v>
+        <v>6168</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>329.6448538230665</v>
+        <v>333.5252251130999</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>37.85</v>
+        <v>26.75</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.71317376009212</v>
+        <v>43.0011118124153</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>12.12193062446123</v>
+        <v>20.85732625886648</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6487112804139489</v>
+        <v>0.1987404294817054</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.1205030778679374</v>
+        <v>-0.5252970654643283</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6228</v>
+        <v>6474</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>319.2400849727944</v>
+        <v>329.6448538230665</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>18.7</v>
+        <v>37.85</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>43.46068281313287</v>
+        <v>51.71317376009212</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>5.157909864093861</v>
+        <v>12.12193062446123</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.0544666280512585</v>
+        <v>0.6487112804139489</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.08468450342489239</v>
+        <v>0.1205030778679374</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6185</v>
+        <v>6228</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>318.575718940834</v>
+        <v>319.2400849727944</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>14.2</v>
+        <v>18.7</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>47.96182090712404</v>
+        <v>43.46068281313287</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.93969103408129</v>
+        <v>5.157909864093861</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.2636925704924341</v>
+        <v>0.0544666280512585</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.0355468210726353</v>
+        <v>-0.08468450342489239</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6266</v>
+        <v>6185</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>309.7694229664768</v>
+        <v>318.575718940834</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>26</v>
+        <v>14.2</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>50.75657116568223</v>
+        <v>47.96182090712404</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>16.75991249207042</v>
+        <v>17.93969103408129</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4210954862157592</v>
+        <v>0.2636925704924341</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.162567212898699</v>
+        <v>-0.0355468210726353</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6415</v>
+        <v>6266</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>307.8848641025102</v>
+        <v>309.7694229664768</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>473</v>
+        <v>26</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>37.66627205792473</v>
+        <v>50.75657116568223</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17.66037729872409</v>
+        <v>16.75991249207042</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.018330592102867</v>
+        <v>0.4210954862157592</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-16.84761985768083</v>
+        <v>0.162567212898699</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6443</v>
+        <v>6415</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>307.5846390191497</v>
+        <v>307.8848641025102</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>29.85</v>
+        <v>473</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>28.24356795700959</v>
+        <v>37.66627205792473</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>23.55634998138066</v>
+        <v>17.66037729872409</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6373886220398077</v>
+        <v>1.018330592102867</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.389451538128184</v>
+        <v>-16.84761985768083</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6234</v>
+        <v>6443</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>306.4075766403083</v>
+        <v>307.5846390191497</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>40</v>
+        <v>29.85</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>40.09858864406067</v>
+        <v>28.24356795700959</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14.5977083623012</v>
+        <v>23.55634998138066</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4693777369604248</v>
+        <v>0.6373886220398077</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.6702163950917954</v>
+        <v>-0.389451538128184</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6237</v>
+        <v>6234</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>306.1217354080181</v>
+        <v>306.4075766403083</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>38.45</v>
+        <v>40</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>32.99427512268582</v>
+        <v>40.09858864406067</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>20.72703696605393</v>
+        <v>14.5977083623012</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.8943475159869139</v>
+        <v>0.4693777369604248</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.6922274556249732</v>
+        <v>-0.6702163950917954</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6438</v>
+        <v>6237</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>302.0195548533405</v>
+        <v>306.1217354080181</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>154.5</v>
+        <v>38.45</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>48.24306179908272</v>
+        <v>32.99427512268582</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>18.8145995386634</v>
+        <v>20.72703696605393</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.4689206917753913</v>
+        <v>0.8943475159869139</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1505715398684683</v>
+        <v>-0.6922274556249732</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6418</v>
+        <v>6438</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>292.238218114438</v>
+        <v>302.0195548533405</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>31.85</v>
+        <v>154.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>48.34381142497388</v>
+        <v>48.24306179908272</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>19.82725421692057</v>
+        <v>18.8145995386634</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3350119031663061</v>
+        <v>0.4689206917753913</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0575590882863897</v>
+        <v>-0.1505715398684683</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6205</v>
+        <v>6418</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>289.8326327334679</v>
+        <v>292.238218114438</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>66.8</v>
+        <v>31.85</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>36.79716088942251</v>
+        <v>48.34381142497388</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.88384732523585</v>
+        <v>19.82725421692057</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3620366942109277</v>
+        <v>0.3350119031663061</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.8717862767893818</v>
+        <v>-0.0575590882863897</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6291</v>
+        <v>6205</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>289.5356766237259</v>
+        <v>289.8326327334679</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>412.5</v>
+        <v>66.8</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,25 +4633,25 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>34.58887600528386</v>
+        <v>36.79716088942251</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>19.79963916951493</v>
+        <v>16.88384732523585</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3238580614058297</v>
+        <v>0.3620366942109277</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-15.59929923283628</v>
+        <v>-0.8717862767893818</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4661,21 +4661,21 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6170</v>
+        <v>6291</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>289.0485581531841</v>
+        <v>289.5356766237259</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>47.2</v>
+        <v>412.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,49 +4686,49 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>25.42532450950725</v>
+        <v>34.58887600528386</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>27.77527620391813</v>
+        <v>19.79963916951493</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4847366600387265</v>
+        <v>0.3238580614058297</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.5919897253983678</v>
+        <v>-15.59929923283628</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6224</v>
+        <v>6170</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>287.4829619493557</v>
+        <v>289.0485581531841</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>63</v>
+        <v>47.2</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>36.9596965193652</v>
+        <v>25.42532450950725</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>18.28440469130824</v>
+        <v>27.77527620391813</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.2564196472515933</v>
+        <v>0.4847366600387265</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-1.985449610404527</v>
+        <v>-0.5919897253983678</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6227</v>
+        <v>6224</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>285.4293437496248</v>
+        <v>287.4829619493557</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>40.27166679070234</v>
+        <v>36.9596965193652</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.84767703408194</v>
+        <v>18.28440469130824</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4489980900945078</v>
+        <v>0.2564196472515933</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-1.20401143980306</v>
+        <v>-1.985449610404527</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6198</v>
+        <v>6227</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>282.954689824229</v>
+        <v>285.4293437496248</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>20.72014987091048</v>
+        <v>40.27166679070234</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>11.19781074124756</v>
+        <v>13.84767703408194</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.0065924565005944</v>
+        <v>0.4489980900945078</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.349101293718007</v>
+        <v>-1.20401143980306</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6456</v>
+        <v>6198</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>278.7815474021141</v>
+        <v>282.954689824229</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>69.7</v>
+        <v>0</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>47.95041433420307</v>
+        <v>20.72014987091048</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16.30202964644758</v>
+        <v>11.19781074124756</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5357176419119702</v>
+        <v>0.0065924565005944</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.2274408263655591</v>
+        <v>-1.349101293718007</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6485</v>
+        <v>6456</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>276.1702172414115</v>
+        <v>278.7815474021141</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>69.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>26.82619391693081</v>
+        <v>47.95041433420307</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>23.36112082661498</v>
+        <v>16.30202964644758</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4913946380850018</v>
+        <v>0.5357176419119702</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.8428615381144269</v>
+        <v>0.2274408263655591</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6188</v>
+        <v>6485</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>267.2716623452318</v>
+        <v>276.1702172414115</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>73.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>35.71382444818269</v>
+        <v>26.82619391693081</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15.08237986538506</v>
+        <v>23.36112082661498</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.4790347590345917</v>
+        <v>0.4913946380850018</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.2248356413324796</v>
+        <v>-0.8428615381144269</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6189</v>
+        <v>6188</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>259.6299660211466</v>
+        <v>267.2716623452318</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>49.05</v>
+        <v>73.7</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>41.50692235751853</v>
+        <v>35.71382444818269</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15.39057793345565</v>
+        <v>15.08237986538506</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.1889978741585293</v>
+        <v>0.4790347590345917</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.4406271787565309</v>
+        <v>-0.2248356413324796</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6206</v>
+        <v>6189</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>259.5412120636459</v>
+        <v>259.6299660211466</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>125</v>
+        <v>49.05</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>42.79476047999345</v>
+        <v>41.50692235751853</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.5174552869335</v>
+        <v>15.39057793345565</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.8061484334132716</v>
+        <v>0.1889978741585293</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.6749231824121118</v>
+        <v>-0.4406271787565309</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5138,38 +5138,38 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6287</v>
+        <v>6206</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>元隆</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>259.3761622103221</v>
+        <v>259.5412120636459</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>125</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G89" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>83.09421130228142</v>
+        <v>42.79476047999345</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v/>
+        <v>14.5174552869335</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.3819364013941486</v>
+        <v>0.8061484334132716</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,84 +5181,84 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.001104545987578</v>
+        <v>-0.6749231824121118</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6290</v>
+        <v>6287</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>元隆</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>256.2254100971844</v>
+        <v>259.3761622103221</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>257.5</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G90" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>32.46615720798411</v>
+        <v>83.09421130228142</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>16.02215630269242</v>
+        <v/>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4709304785606231</v>
+        <v>0.3819364013941486</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-6.299064410297797</v>
+        <v>0.001104545987578</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6222</v>
+        <v>6290</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>251.6444641803949</v>
+        <v>256.2254100971844</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>20.45</v>
+        <v>257.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,49 +5269,49 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>44.82068881729478</v>
+        <v>32.46615720798411</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>20.9222757206219</v>
+        <v>16.02215630269242</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.4815812375949833</v>
+        <v>0.4709304785606231</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0073175940680579</v>
+        <v>-6.299064410297797</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6263</v>
+        <v>6222</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>251.3245997354537</v>
+        <v>251.6444641803949</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>158</v>
+        <v>20.45</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>44.25368092647336</v>
+        <v>44.82068881729478</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11.43211793945774</v>
+        <v>20.9222757206219</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4335287878601737</v>
+        <v>0.4815812375949833</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.8236997263458637</v>
+        <v>0.0073175940680579</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6412</v>
+        <v>6263</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>249.9910654801476</v>
+        <v>251.3245997354537</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>83.5</v>
+        <v>158</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>36.38664724000522</v>
+        <v>44.25368092647336</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>17.11783882933166</v>
+        <v>11.43211793945774</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3664439873762509</v>
+        <v>0.4335287878601737</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-1.070612649577851</v>
+        <v>-0.8236997263458637</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6239</v>
+        <v>6412</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>249.7117785914498</v>
+        <v>249.9910654801476</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>316.5</v>
+        <v>83.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>48.16907450223036</v>
+        <v>36.38664724000522</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>19.11214187080227</v>
+        <v>17.11783882933166</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4224301443563313</v>
+        <v>0.3664439873762509</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-4.435329543113836</v>
+        <v>-1.070612649577851</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5456,21 +5456,21 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6246</v>
+        <v>6239</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>238.5308147688349</v>
+        <v>249.7117785914498</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>14.7</v>
+        <v>316.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>39.78647695932703</v>
+        <v>48.16907450223036</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17.19753360552131</v>
+        <v>19.11214187080227</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.2585267817580553</v>
+        <v>0.4224301443563313</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.119901504176429</v>
+        <v>-4.435329543113836</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6292</v>
+        <v>6246</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>236.1239374180657</v>
+        <v>238.5308147688349</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>53</v>
+        <v>14.7</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>38.08895967923162</v>
+        <v>39.78647695932703</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>19.40867238002813</v>
+        <v>17.19753360552131</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.2491853511693558</v>
+        <v>0.2585267817580553</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-1.22572737962392</v>
+        <v>-0.119901504176429</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6405</v>
+        <v>6292</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>234.5998252222224</v>
+        <v>236.1239374180657</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>48.4</v>
+        <v>53</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>32.29680540329282</v>
+        <v>38.08895967923162</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>18.15994821420547</v>
+        <v>19.40867238002813</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4787697122797894</v>
+        <v>0.2491853511693558</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-1.477879859637852</v>
+        <v>-1.22572737962392</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6272</v>
+        <v>6405</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>223.3280995537559</v>
+        <v>234.5998252222224</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>28.7</v>
+        <v>48.4</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>34.9160284924461</v>
+        <v>32.29680540329282</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>20.36966221211166</v>
+        <v>18.15994821420547</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8242805476115043</v>
+        <v>0.4787697122797894</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.2457885183326953</v>
+        <v>-1.477879859637852</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6216</v>
+        <v>6272</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>218.9525210137922</v>
+        <v>223.3280995537559</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>22.6</v>
+        <v>28.7</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>45.65023850370948</v>
+        <v>34.9160284924461</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.09016075334813</v>
+        <v>20.36966221211166</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5605177956902543</v>
+        <v>0.8242805476115043</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0186570115207374</v>
+        <v>-0.2457885183326953</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6194</v>
+        <v>6216</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>215.1563932297022</v>
+        <v>218.9525210137922</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>31.4</v>
+        <v>22.6</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>39.96614530331695</v>
+        <v>45.65023850370948</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18.44702796634641</v>
+        <v>13.09016075334813</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.3825015477719209</v>
+        <v>0.5605177956902543</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.1009374362413736</v>
+        <v>-0.0186570115207374</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5774,21 +5774,21 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6225</v>
+        <v>6194</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>211.9228138874799</v>
+        <v>215.1563932297022</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>25.55</v>
+        <v>31.4</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>59.19417537383123</v>
+        <v>39.96614530331695</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>15.6423465846167</v>
+        <v>18.44702796634641</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.132729339228398</v>
+        <v>0.3825015477719209</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.4909167256545204</v>
+        <v>-0.1009374362413736</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6269</v>
+        <v>6225</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>210.3849181562322</v>
+        <v>211.9228138874799</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>61.1</v>
+        <v>25.55</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>40.48632401552683</v>
+        <v>59.19417537383123</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>15.76728201317759</v>
+        <v>15.6423465846167</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3850720027588317</v>
+        <v>1.132729339228398</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-1.24245372021464</v>
+        <v>0.4909167256545204</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6167</v>
+        <v>6269</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>207.2889637153746</v>
+        <v>210.3849181562322</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>11.45</v>
+        <v>61.1</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>41.88631790262198</v>
+        <v>40.48632401552683</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>10.92221080353638</v>
+        <v>15.76728201317759</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.2726624243622631</v>
+        <v>0.3850720027588317</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.07593558395322279</v>
+        <v>-1.24245372021464</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6176</v>
+        <v>6167</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>204.2422948574612</v>
+        <v>207.2889637153746</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>88.59999999999999</v>
+        <v>11.45</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>41.79783831655397</v>
+        <v>41.88631790262198</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>16.95365631878741</v>
+        <v>10.92221080353638</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.4555770358843505</v>
+        <v>0.2726624243622631</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.3477826267563972</v>
+        <v>-0.07593558395322279</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6230</v>
+        <v>6176</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>188.777202022878</v>
+        <v>204.2422948574612</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>118</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>37.0666537193642</v>
+        <v>41.79783831655397</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>23.17440951665398</v>
+        <v>16.95365631878741</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.7575852584233101</v>
+        <v>0.4555770358843505</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.215174429086991</v>
+        <v>0.3477826267563972</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6281</v>
+        <v>6230</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>187.4862820762805</v>
+        <v>188.777202022878</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>51.6</v>
+        <v>118</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>51.65355481956944</v>
+        <v>37.0666537193642</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>10.62346810936717</v>
+        <v>23.17440951665398</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4085996686312667</v>
+        <v>0.7575852584233101</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0092361653762444</v>
+        <v>-0.215174429086991</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6233</v>
+        <v>6281</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>185.2733037924126</v>
+        <v>187.4862820762805</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>24.35</v>
+        <v>51.6</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46.00221874446203</v>
+        <v>51.65355481956944</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>14.37758100220453</v>
+        <v>10.62346810936717</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5223423896325999</v>
+        <v>0.4085996686312667</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.1020130977173418</v>
+        <v>0.0092361653762444</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6184</v>
+        <v>6233</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>183.8935311092092</v>
+        <v>185.2733037924126</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>42.95</v>
+        <v>24.35</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>28.62045098487533</v>
+        <v>46.00221874446203</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>32.36123446468179</v>
+        <v>14.37758100220453</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3449273084479371</v>
+        <v>0.5223423896325999</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0080199655184212</v>
+        <v>-0.1020130977173418</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6236</v>
+        <v>6184</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>179.0884570524432</v>
+        <v>183.8935311092092</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>0</v>
+        <v>42.95</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>48.11588855825985</v>
+        <v>28.62045098487533</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>6.670554261137346</v>
+        <v>32.36123446468179</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0</v>
+        <v>0.3449273084479371</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.3906736815219457</v>
+        <v>-0.0080199655184212</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6276</v>
+        <v>6236</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>160.6827736702767</v>
+        <v>179.0884570524432</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>35.86814313329755</v>
+        <v>48.11588855825985</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>28.08261179581126</v>
+        <v>6.670554261137346</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.1378691538627639</v>
+        <v>0</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1497359570029512</v>
+        <v>-0.3906736815219457</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6462</v>
+        <v>6276</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>160.1472751645039</v>
+        <v>160.6827736702767</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>101.5</v>
+        <v>21.7</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>34.09605387969002</v>
+        <v>35.86814313329755</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>18.26399164613938</v>
+        <v>28.08261179581126</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.3528986881764159</v>
+        <v>0.1378691538627639</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-1.46035153400349</v>
+        <v>0.1497359570029512</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6470</v>
+        <v>6462</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>132.6768733943009</v>
+        <v>160.1472751645039</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>47.9</v>
+        <v>101.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>42.28117200922736</v>
+        <v>34.09605387969002</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>12.00886317600925</v>
+        <v>18.26399164613938</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.1029682270045332</v>
+        <v>0.3528986881764159</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1856208440303706</v>
+        <v>-1.46035153400349</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6283</v>
+        <v>6470</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>121.9726957822269</v>
+        <v>132.6768733943009</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>21.85</v>
+        <v>47.9</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>37.36852732061881</v>
+        <v>42.28117200922736</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.15747371239598</v>
+        <v>12.00886317600925</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.2777177544716822</v>
+        <v>0.1029682270045332</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.2074333833666959</v>
+        <v>-0.1856208440303706</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6275</v>
+        <v>6283</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>111.2669038940456</v>
+        <v>121.9726957822269</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>47.2</v>
+        <v>21.85</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.58703918821637</v>
+        <v>37.36852732061881</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>12.76254801151571</v>
+        <v>16.15747371239598</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.1753267939908122</v>
+        <v>0.2777177544716822</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.2341465400854424</v>
+        <v>-0.2074333833666959</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6203</v>
+        <v>6275</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>110.5573493754987</v>
+        <v>111.2669038940456</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>65</v>
+        <v>47.2</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>37.4133210395518</v>
+        <v>42.58703918821637</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>13.22584517800213</v>
+        <v>12.76254801151571</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.7580914812979471</v>
+        <v>0.1753267939908122</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.1319917448726675</v>
+        <v>-0.2341465400854424</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,52 +6569,105 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>海韻電</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>110.5573493754987</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>37.4133210395518</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>13.22584517800213</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.7580914812979471</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.1319917448726675</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
         <v>6441</v>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>廣錠</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="n">
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>80.23896098226368</v>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E117" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
         <v>43.60406027290221</v>
       </c>
-      <c r="I116" s="2" t="n">
+      <c r="I117" s="2" t="n">
         <v>11.63362279295164</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J117" s="2" t="n">
         <v>0.1570463370531163</v>
       </c>
-      <c r="K116" s="2" t="n">
+      <c r="K117" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" s="2" t="n">
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
         <v>-0.0014889875131823</v>
       </c>
-      <c r="O116" s="2" t="inlineStr">
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
